--- a/hw03/truthtable.xlsx
+++ b/hw03/truthtable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10514"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gtvault-my.sharepoint.com/personal/zakkawi3_gatech_edu/Documents/Desktop/Georgia Tech/Spring 2023/CS 2110/hw03 revisions/HW-StateMachines/student/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\huan\Documents\GT\Summer 2023\CS_2110\hw03\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="85" documentId="13_ncr:1_{B6882957-55CA-E549-BA7E-922E3ECC9EF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{40682341-3628-394D-90E8-C692C5DFCF03}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38CD1BB1-62DC-435E-8A50-C4D2F6B0752D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="15080" windowHeight="15840" xr2:uid="{AF1E79C0-038F-4BC8-AE45-4A93FB27711B}"/>
+    <workbookView xWindow="3375" yWindow="-16200" windowWidth="14610" windowHeight="15585" xr2:uid="{AF1E79C0-038F-4BC8-AE45-4A93FB27711B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -150,10 +150,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -454,9 +450,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{055CBB65-E912-4CBB-9BAF-9C2E3282BA2C}">
   <dimension ref="A1:H9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -482,7 +478,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="3">
         <v>0</v>
       </c>
@@ -492,13 +488,23 @@
       <c r="C2" s="3">
         <v>0</v>
       </c>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D2" s="4">
+        <v>0</v>
+      </c>
+      <c r="E2" s="4">
+        <v>1</v>
+      </c>
+      <c r="F2" s="4">
+        <v>1</v>
+      </c>
+      <c r="G2" s="4">
+        <v>0</v>
+      </c>
+      <c r="H2" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <v>0</v>
       </c>
@@ -508,13 +514,23 @@
       <c r="C3" s="3">
         <v>1</v>
       </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D3" s="4">
+        <v>0</v>
+      </c>
+      <c r="E3" s="4">
+        <v>1</v>
+      </c>
+      <c r="F3" s="4">
+        <v>1</v>
+      </c>
+      <c r="G3" s="4">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <v>0</v>
       </c>
@@ -524,13 +540,23 @@
       <c r="C4" s="3">
         <v>0</v>
       </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D4" s="4">
+        <v>1</v>
+      </c>
+      <c r="E4" s="4">
+        <v>0</v>
+      </c>
+      <c r="F4" s="4">
+        <v>1</v>
+      </c>
+      <c r="G4" s="4">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>0</v>
       </c>
@@ -540,13 +566,23 @@
       <c r="C5" s="3">
         <v>1</v>
       </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D5" s="4">
+        <v>0</v>
+      </c>
+      <c r="E5" s="4">
+        <v>1</v>
+      </c>
+      <c r="F5" s="4">
+        <v>1</v>
+      </c>
+      <c r="G5" s="4">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>1</v>
       </c>
@@ -556,13 +592,23 @@
       <c r="C6" s="3">
         <v>0</v>
       </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D6" s="4">
+        <v>1</v>
+      </c>
+      <c r="E6" s="4">
+        <v>1</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4">
+        <v>1</v>
+      </c>
+      <c r="H6" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>1</v>
       </c>
@@ -572,13 +618,23 @@
       <c r="C7" s="3">
         <v>1</v>
       </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D7" s="4">
+        <v>0</v>
+      </c>
+      <c r="E7" s="4">
+        <v>1</v>
+      </c>
+      <c r="F7" s="4">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4">
+        <v>1</v>
+      </c>
+      <c r="H7" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>1</v>
       </c>
@@ -588,13 +644,23 @@
       <c r="C8" s="3">
         <v>0</v>
       </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D8" s="4">
+        <v>0</v>
+      </c>
+      <c r="E8" s="4">
+        <v>0</v>
+      </c>
+      <c r="F8" s="4">
+        <v>1</v>
+      </c>
+      <c r="G8" s="4">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>1</v>
       </c>
@@ -604,11 +670,21 @@
       <c r="C9" s="3">
         <v>1</v>
       </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
+      <c r="D9" s="4">
+        <v>0</v>
+      </c>
+      <c r="E9" s="4">
+        <v>0</v>
+      </c>
+      <c r="F9" s="4">
+        <v>1</v>
+      </c>
+      <c r="G9" s="4">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
